--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBAC3BD-46B5-4B78-8E3D-768F815985EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006BC555-E51D-4C44-8681-C774BEA71D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,35 +608,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Заказы</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ru-RU" baseline="0"/>
-              <a:t> по регионам</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -667,9 +638,48 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
+      <c:bar3DChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
@@ -695,18 +705,12 @@
               <a:noFill/>
             </a:ln>
             <a:effectLst/>
+            <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>States!$A$2:$B$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>States!$A$2:$B$6</c:f>
+              <c:f>States!$A$2:$B$8</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="5"/>
                 <c:lvl>
@@ -748,17 +752,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>States!$B$2:$B$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>States!$B$2:$B$6</c:f>
+              <c:f>States!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>21073</c:v>
                 </c:pt>
@@ -779,7 +776,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-15ED-4E77-98AC-5952B554B6C7}"/>
+              <c16:uniqueId val="{00000000-3AC1-4945-B39D-F56E6A8EA8C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -791,10 +788,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="425813855"/>
-        <c:axId val="425802335"/>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="1555498832"/>
+        <c:axId val="1555497392"/>
+        <c:axId val="0"/>
         <c:extLst>
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredBarSeries>
@@ -826,17 +824,15 @@
                     <a:noFill/>
                   </a:ln>
                   <a:effectLst/>
+                  <a:sp3d/>
                 </c:spPr>
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>States!$A$2:$B$7</c15:sqref>
-                        </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>States!$A$2:$B$6</c15:sqref>
+                          <c15:sqref>States!$A$2:$B$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -883,17 +879,14 @@
                   <c:numRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
+                        <c15:formulaRef>
                           <c15:sqref>States!$A$2:$A$7</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>States!$A$2:$A$6</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="6"/>
                       <c:pt idx="0">
                         <c:v>0</c:v>
                       </c:pt>
@@ -914,16 +907,16 @@
                 </c:val>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-15ED-4E77-98AC-5952B554B6C7}"/>
+                    <c16:uniqueId val="{00000001-3AC1-4945-B39D-F56E6A8EA8C7}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
             </c15:filteredBarSeries>
           </c:ext>
         </c:extLst>
-      </c:barChart>
+      </c:bar3DChart>
       <c:catAx>
-        <c:axId val="425813855"/>
+        <c:axId val="1555498832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -935,14 +928,8 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -966,7 +953,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="425802335"/>
+        <c:crossAx val="1555497392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -974,7 +961,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="425802335"/>
+        <c:axId val="1555497392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1025,7 +1012,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="425813855"/>
+        <c:crossAx val="1555498832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1652,22 +1639,22 @@
                 <c:ptCount val="7"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>788.94</c:v>
+                    <c:v>788,94</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>764.42</c:v>
+                    <c:v>764,42</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>724.37</c:v>
+                    <c:v>724,37</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>536.94</c:v>
+                    <c:v>536,94</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>534.73</c:v>
+                    <c:v>534,73</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>449.32</c:v>
+                    <c:v>449,32</c:v>
                   </c:pt>
                   <c:pt idx="6">
                     <c:v>352</c:v>
@@ -1805,22 +1792,22 @@
                       <c:ptCount val="7"/>
                       <c:lvl>
                         <c:pt idx="0">
-                          <c:v>788.94</c:v>
+                          <c:v>788,94</c:v>
                         </c:pt>
                         <c:pt idx="1">
-                          <c:v>764.42</c:v>
+                          <c:v>764,42</c:v>
                         </c:pt>
                         <c:pt idx="2">
-                          <c:v>724.37</c:v>
+                          <c:v>724,37</c:v>
                         </c:pt>
                         <c:pt idx="3">
-                          <c:v>536.94</c:v>
+                          <c:v>536,94</c:v>
                         </c:pt>
                         <c:pt idx="4">
-                          <c:v>534.73</c:v>
+                          <c:v>534,73</c:v>
                         </c:pt>
                         <c:pt idx="5">
-                          <c:v>449.32</c:v>
+                          <c:v>449,32</c:v>
                         </c:pt>
                         <c:pt idx="6">
                           <c:v>352</c:v>
@@ -2726,35 +2713,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Заказы</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ru-RU" baseline="0"/>
-              <a:t> по регионам</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2785,9 +2743,48 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
+      <c:bar3DChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
@@ -2813,18 +2810,12 @@
               <a:noFill/>
             </a:ln>
             <a:effectLst/>
+            <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>States!$A$2:$B$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>States!$A$2:$B$6</c:f>
+              <c:f>States!$A$2:$B$8</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="5"/>
                 <c:lvl>
@@ -2866,17 +2857,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>States!$B$2:$B$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>States!$B$2:$B$6</c:f>
+              <c:f>States!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>21073</c:v>
                 </c:pt>
@@ -2897,7 +2881,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E1C8-4FFE-91D1-16374849F4D3}"/>
+              <c16:uniqueId val="{00000001-5A50-4E13-B47E-50DE200338C4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2909,10 +2893,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="425813855"/>
-        <c:axId val="425802335"/>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="1555498832"/>
+        <c:axId val="1555497392"/>
+        <c:axId val="0"/>
         <c:extLst>
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredBarSeries>
@@ -2944,17 +2929,15 @@
                     <a:noFill/>
                   </a:ln>
                   <a:effectLst/>
+                  <a:sp3d/>
                 </c:spPr>
                 <c:invertIfNegative val="0"/>
                 <c:cat>
                   <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>States!$A$2:$B$7</c15:sqref>
-                        </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>States!$A$2:$B$6</c15:sqref>
+                          <c15:sqref>States!$A$2:$B$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -3001,17 +2984,14 @@
                   <c:numRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
+                        <c15:formulaRef>
                           <c15:sqref>States!$A$2:$A$7</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>States!$A$2:$A$6</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="6"/>
                       <c:pt idx="0">
                         <c:v>0</c:v>
                       </c:pt>
@@ -3032,16 +3012,16 @@
                 </c:val>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000000-E1C8-4FFE-91D1-16374849F4D3}"/>
+                    <c16:uniqueId val="{00000000-5A50-4E13-B47E-50DE200338C4}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
             </c15:filteredBarSeries>
           </c:ext>
         </c:extLst>
-      </c:barChart>
+      </c:bar3DChart>
       <c:catAx>
-        <c:axId val="425813855"/>
+        <c:axId val="1555498832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3053,14 +3033,8 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3084,7 +3058,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="425802335"/>
+        <c:crossAx val="1555497392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3092,7 +3066,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="425802335"/>
+        <c:axId val="1555497392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3143,7 +3117,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="425813855"/>
+        <c:crossAx val="1555498832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6105,7 +6079,7 @@
 </file>
 
 <file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6128,17 +6102,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
@@ -6309,22 +6272,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6429,8 +6393,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6562,19 +6526,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -8099,7 +8064,7 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8122,17 +8087,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
@@ -8303,22 +8257,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -8423,8 +8378,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8556,19 +8511,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -10763,23 +10719,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>85724</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Диаграмма 1">
+        <xdr:cNvPr id="3" name="Диаграмма 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDBEBC81-9AFA-272A-B4D6-4821AD5CE867}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B6699D2-5B4C-C40D-4C0E-6CF515B83D9A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10811,9 +10767,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10843,15 +10799,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10919,15 +10875,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10959,20 +10915,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Диаграмма 7">
+        <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5DB1B77-FEFF-41E9-BCA8-B80E3A1383A5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC477A1-0FCD-43EB-A43C-802E5BE9A0F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
